--- a/docs/data/treasury-scope-items.xlsx
+++ b/docs/data/treasury-scope-items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanRuman\Downloads\Public Cloud\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE7BFFF9-A830-4D70-99C2-B1514ED0F406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05573D53-60D4-4D76-ABAC-813880D99580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11919" uniqueCount="1768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11919" uniqueCount="1769">
   <si>
     <t>Erweiterte Bankkontenverwaltung (J77)</t>
   </si>
@@ -5356,6 +5356,9 @@
   </si>
   <si>
     <t>SAP Finance Base</t>
+  </si>
+  <si>
+    <t>SAP Multi-Bank Connectivity (recommended)</t>
   </si>
 </sst>
 </file>
@@ -5847,7 +5850,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5857,7 +5859,7 @@
     <col min="4" max="4" width="20.88671875" customWidth="1"/>
     <col min="5" max="5" width="30.21875" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="57.109375" customWidth="1"/>
     <col min="8" max="8" width="22.5546875" customWidth="1"/>
     <col min="9" max="10" width="10.109375" customWidth="1"/>
     <col min="11" max="11" width="26.109375" customWidth="1"/>
@@ -5906,7 +5908,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -5937,7 +5939,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
@@ -5968,7 +5970,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
@@ -5984,7 +5986,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8" t="s">
-        <v>621</v>
+        <v>1768</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>622</v>
@@ -6003,7 +6005,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -6143,7 +6145,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -6178,7 +6180,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -6316,7 +6318,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>24</v>
       </c>
@@ -6347,7 +6349,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>26</v>
       </c>
@@ -6382,7 +6384,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>28</v>
       </c>
@@ -6413,7 +6415,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>30</v>
       </c>
@@ -6444,7 +6446,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
@@ -6975,7 +6977,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>62</v>
       </c>
@@ -7195,7 +7197,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="46.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>74</v>
       </c>
@@ -7479,7 +7481,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="38.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>90</v>
       </c>
@@ -8051,7 +8053,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="44.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>122</v>
       </c>
@@ -8123,7 +8125,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>126</v>
       </c>
@@ -8191,20 +8193,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K70" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M70" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" tooltip="Erweiterte Bankkontenverwaltung (J77)" display="https://me.sap.com/processnavigator/SolS/EARL_SolS-013/2602/SolP/J77/?region=DE" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A3" r:id="rId2" tooltip="Erweiterte Kassenvorgänge (J78)" display="https://me.sap.com/processnavigator/SolS/EARL_SolS-013/2602/SolP/J78/?region=DE" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
